--- a/data/trans_orig/IP31C_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_R_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20996</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14845</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30008</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11702</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6830</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18804</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91201</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>106364</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>90007</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82905</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>94879</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114450</t>
+          <t>88095</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>204457</t>
+          <t>188308</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194748</t>
+          <t>178136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213060</t>
+          <t>196212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86438</t>
+          <t>75278</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89836</t>
+          <t>80720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>124</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79941</t>
+          <t>85423</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73669</t>
+          <t>79310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85008</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>166378</t>
+          <t>160702</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159223</t>
+          <t>151391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>167619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8546</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13098</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51960</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47298</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54527</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42380</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36322</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46088</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60869</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>95285</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93604</t>
+          <t>85682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105402</t>
+          <t>100175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>46961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1867,102 +1867,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202750</t>
+          <t>182248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194879</t>
+          <t>174292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208667</t>
+          <t>188130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>249</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>200098</t>
+          <t>157524</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192728</t>
+          <t>146394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>503</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>402849</t>
+          <t>339772</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391972</t>
+          <t>326992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410938</t>
+          <t>349280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11523</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20821</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6220</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11889</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133201</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123903</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>138443</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>109289</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>103620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112503</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>150790</t>
+          <t>108856</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143976</t>
+          <t>102968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154945</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>341</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>260079</t>
+          <t>242057</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251763</t>
+          <t>232777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265722</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13228</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5765</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>58534</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52635</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62229</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>66316</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>62583</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67976</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62462</t>
+          <t>67836</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65949</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>128778</t>
+          <t>126370</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>118971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132746</t>
+          <t>130663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>72509</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>57539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58335</t>
+          <t>88077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64318</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80275</t>
+          <t>71901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>163</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>110668</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93147</t>
+          <t>110330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130659</t>
+          <t>149693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>827</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>597180</t>
+          <t>601434</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585195</t>
+          <t>585866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608693</t>
+          <t>616404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>829</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>666127</t>
+          <t>551059</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>650170</t>
+          <t>536872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679428</t>
+          <t>563524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1263307</t>
+          <t>1152493</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1243316</t>
+          <t>1133023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1280828</t>
+          <t>1172386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
